--- a/soulia/tableau_clean.xlsx
+++ b/soulia/tableau_clean.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\francesco.monti\Documents\GitHub\theses_internes\soulia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Documents\Git\tesi_internes\soulia\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76A2C1F-361B-4D28-95BA-9FD7E32690E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -20,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$C$1:$C$369</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5244" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5245" uniqueCount="572">
   <si>
     <t>Sexe</t>
   </si>
@@ -1763,7 +1764,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="36">
     <font>
       <sz val="11"/>
@@ -3349,22 +3350,22 @@
     </xf>
   </cellXfs>
   <cellStyles count="16">
-    <cellStyle name="20 % - Accent1" xfId="2" builtinId="30"/>
-    <cellStyle name="40 % - Accent2" xfId="5" builtinId="35"/>
-    <cellStyle name="40 % - Accent5" xfId="8" builtinId="47"/>
-    <cellStyle name="40 % - Accent6" xfId="11" builtinId="51"/>
-    <cellStyle name="60 % - Accent1" xfId="3" builtinId="32"/>
-    <cellStyle name="60 % - Accent2" xfId="6" builtinId="36"/>
-    <cellStyle name="60 % - Accent5" xfId="9" builtinId="48"/>
-    <cellStyle name="60 % - Accent6" xfId="12" builtinId="52"/>
-    <cellStyle name="Accent1" xfId="1" builtinId="29"/>
-    <cellStyle name="Accent2" xfId="4" builtinId="33"/>
-    <cellStyle name="Accent5" xfId="7" builtinId="45"/>
-    <cellStyle name="Accent6" xfId="10" builtinId="49"/>
-    <cellStyle name="Lien hypertexte" xfId="13" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="14"/>
-    <cellStyle name="Normal 3" xfId="15"/>
+    <cellStyle name="20% - Colore 1" xfId="2" builtinId="30"/>
+    <cellStyle name="40% - Colore 2" xfId="5" builtinId="35"/>
+    <cellStyle name="40% - Colore 5" xfId="8" builtinId="47"/>
+    <cellStyle name="40% - Colore 6" xfId="11" builtinId="51"/>
+    <cellStyle name="60% - Colore 1" xfId="3" builtinId="32"/>
+    <cellStyle name="60% - Colore 2" xfId="6" builtinId="36"/>
+    <cellStyle name="60% - Colore 5" xfId="9" builtinId="48"/>
+    <cellStyle name="60% - Colore 6" xfId="12" builtinId="52"/>
+    <cellStyle name="Collegamento ipertestuale" xfId="13" builtinId="8"/>
+    <cellStyle name="Colore 1" xfId="1" builtinId="29"/>
+    <cellStyle name="Colore 2" xfId="4" builtinId="33"/>
+    <cellStyle name="Colore 5" xfId="7" builtinId="45"/>
+    <cellStyle name="Colore 6" xfId="10" builtinId="49"/>
+    <cellStyle name="Normal 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Normal 3" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3689,10 +3690,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Foglio1" filterMode="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Foglio1"/>
   <dimension ref="A1:DC369"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.6640625" style="4" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" style="171" customWidth="1"/>
@@ -4041,7 +4042,7 @@
       <c r="CK1" s="163"/>
       <c r="CL1" s="164"/>
     </row>
-    <row r="2" spans="1:90" ht="29.4" hidden="1" thickTop="1">
+    <row r="2" spans="1:90" ht="29.4" thickTop="1">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -4151,7 +4152,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:90" ht="29.4" hidden="1" thickTop="1">
+    <row r="3" spans="1:90" ht="28.8">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -4262,7 +4263,7 @@
       </c>
       <c r="AW3" s="1">
         <f t="shared" ref="AW3:AW66" ca="1" si="2">DATEDIF(AV3,TODAY(),"Y")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX3" s="1" t="s">
         <v>445</v>
@@ -4286,7 +4287,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:90" ht="15" hidden="1" thickTop="1">
+    <row r="4" spans="1:90">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -4440,7 +4441,7 @@
       <c r="BU4" s="167"/>
       <c r="CE4" s="167"/>
     </row>
-    <row r="5" spans="1:90" ht="15" hidden="1" thickTop="1">
+    <row r="5" spans="1:90">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -4580,7 +4581,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:90" ht="15" hidden="1" thickTop="1">
+    <row r="6" spans="1:90">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -4595,7 +4596,7 @@
       </c>
       <c r="E6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F6" s="1">
         <f t="shared" si="1"/>
@@ -4697,7 +4698,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:90" ht="15" hidden="1" thickTop="1">
+    <row r="7" spans="1:90">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -4841,7 +4842,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:90" ht="15" hidden="1" thickTop="1">
+    <row r="8" spans="1:90">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -4910,7 +4911,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:90" ht="15" hidden="1" thickTop="1">
+    <row r="9" spans="1:90">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -4973,7 +4974,7 @@
       <c r="BU9" s="167"/>
       <c r="CE9" s="167"/>
     </row>
-    <row r="10" spans="1:90" ht="15" hidden="1" thickTop="1">
+    <row r="10" spans="1:90">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -5120,7 +5121,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="1:90" ht="15" hidden="1" thickTop="1">
+    <row r="11" spans="1:90">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -5189,7 +5190,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:90" ht="15" hidden="1" thickTop="1">
+    <row r="12" spans="1:90">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -5253,7 +5254,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:90" ht="15" hidden="1" thickTop="1">
+    <row r="13" spans="1:90">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -5358,7 +5359,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="1:90" ht="15" hidden="1" thickTop="1">
+    <row r="14" spans="1:90">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -5474,7 +5475,7 @@
       <c r="BU14" s="167"/>
       <c r="CE14" s="167"/>
     </row>
-    <row r="15" spans="1:90" ht="15" hidden="1" thickTop="1">
+    <row r="15" spans="1:90">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -5582,7 +5583,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="16" spans="1:90" ht="15" hidden="1" thickTop="1">
+    <row r="16" spans="1:90">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -5693,7 +5694,7 @@
       <c r="BU16" s="167"/>
       <c r="CE16" s="167"/>
     </row>
-    <row r="17" spans="1:89" ht="15" hidden="1" thickTop="1">
+    <row r="17" spans="1:89">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -5818,7 +5819,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:89" ht="15" hidden="1" thickTop="1">
+    <row r="18" spans="1:89">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -5863,7 +5864,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="19" spans="1:89" ht="15" hidden="1" thickTop="1">
+    <row r="19" spans="1:89">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -5908,7 +5909,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="20" spans="1:89" ht="15" hidden="1" thickTop="1">
+    <row r="20" spans="1:89">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -5953,7 +5954,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="21" spans="1:89" ht="15" hidden="1" thickTop="1">
+    <row r="21" spans="1:89">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -6001,7 +6002,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="22" spans="1:89" ht="15" hidden="1" thickTop="1">
+    <row r="22" spans="1:89">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -6118,7 +6119,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:89" ht="15" hidden="1" thickTop="1">
+    <row r="23" spans="1:89">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -6178,7 +6179,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:89" ht="15" hidden="1" thickTop="1">
+    <row r="24" spans="1:89">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -6250,7 +6251,7 @@
       <c r="BU24" s="167"/>
       <c r="CE24" s="167"/>
     </row>
-    <row r="25" spans="1:89" ht="15" hidden="1" thickTop="1">
+    <row r="25" spans="1:89">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -6370,7 +6371,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="1:89" ht="15" hidden="1" thickTop="1">
+    <row r="26" spans="1:89">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -6409,7 +6410,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="27" spans="1:89" ht="15" hidden="1" thickTop="1">
+    <row r="27" spans="1:89">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -6525,7 +6526,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:89" ht="15" hidden="1" thickTop="1">
+    <row r="28" spans="1:89">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -6624,7 +6625,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:89" ht="15" hidden="1" thickTop="1">
+    <row r="29" spans="1:89">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -6721,7 +6722,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="30" spans="1:89" ht="15" hidden="1" thickTop="1">
+    <row r="30" spans="1:89">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -6838,7 +6839,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="1:89" ht="15" hidden="1" thickTop="1">
+    <row r="31" spans="1:89">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -6902,7 +6903,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="32" spans="1:89" ht="15" hidden="1" thickTop="1">
+    <row r="32" spans="1:89">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -7045,7 +7046,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:90" ht="15" hidden="1" thickTop="1">
+    <row r="33" spans="1:90">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -7155,7 +7156,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="34" spans="1:90" ht="15" hidden="1" thickTop="1">
+    <row r="34" spans="1:90">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -7281,7 +7282,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:90" ht="15" hidden="1" thickTop="1">
+    <row r="35" spans="1:90">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -7417,7 +7418,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="36" spans="1:90" ht="15" hidden="1" thickTop="1">
+    <row r="36" spans="1:90">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -7506,7 +7507,7 @@
       </c>
       <c r="AW36" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX36" s="1" t="s">
         <v>445</v>
@@ -7524,7 +7525,7 @@
       <c r="BU36" s="167"/>
       <c r="CE36" s="167"/>
     </row>
-    <row r="37" spans="1:90" ht="15" thickTop="1">
+    <row r="37" spans="1:90">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -7997,7 +7998,7 @@
       </c>
       <c r="AW40" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX40" s="1" t="s">
         <v>444</v>
@@ -9641,7 +9642,7 @@
       </c>
       <c r="E53" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F53" s="1">
         <f t="shared" si="3"/>
@@ -9981,8 +9982,8 @@
         <v>0</v>
       </c>
       <c r="AB56" s="166"/>
-      <c r="AC56" s="1">
-        <v>4.5</v>
+      <c r="AC56" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="AF56" s="167" t="s">
         <v>150</v>
@@ -12357,7 +12358,7 @@
       </c>
       <c r="AW75" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX75" s="1" t="s">
         <v>445</v>
@@ -12920,7 +12921,7 @@
       </c>
       <c r="AW80" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX80" s="1" t="s">
         <v>63</v>
@@ -14182,7 +14183,7 @@
       </c>
       <c r="AW91" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX91" s="1" t="s">
         <v>63</v>
@@ -14631,7 +14632,7 @@
       </c>
       <c r="AW95" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX95" s="1" t="s">
         <v>445</v>
@@ -15056,7 +15057,7 @@
       </c>
       <c r="E99" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F99" s="1">
         <f t="shared" si="7"/>
@@ -17002,7 +17003,7 @@
       </c>
       <c r="AW115" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX115" s="1" t="s">
         <v>445</v>
@@ -18496,7 +18497,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="128" spans="1:87" hidden="1">
+    <row r="128" spans="1:87">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -18589,7 +18590,7 @@
       </c>
       <c r="CE128" s="167"/>
     </row>
-    <row r="129" spans="1:87" hidden="1">
+    <row r="129" spans="1:87">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -18750,7 +18751,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="130" spans="1:87" hidden="1">
+    <row r="130" spans="1:87">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -18907,7 +18908,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="131" spans="1:87" hidden="1">
+    <row r="131" spans="1:87">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -19038,7 +19039,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="132" spans="1:87" hidden="1">
+    <row r="132" spans="1:87">
       <c r="A132" s="4">
         <v>131</v>
       </c>
@@ -19172,7 +19173,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="133" spans="1:87" hidden="1">
+    <row r="133" spans="1:87">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -19315,7 +19316,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="134" spans="1:87" hidden="1">
+    <row r="134" spans="1:87">
       <c r="A134" s="4">
         <v>133</v>
       </c>
@@ -19472,7 +19473,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="135" spans="1:87" hidden="1">
+    <row r="135" spans="1:87">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -19628,7 +19629,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="136" spans="1:87" hidden="1">
+    <row r="136" spans="1:87">
       <c r="A136" s="4">
         <v>135</v>
       </c>
@@ -19786,7 +19787,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="137" spans="1:87" ht="28.8" hidden="1">
+    <row r="137" spans="1:87" ht="28.8">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -19937,7 +19938,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="138" spans="1:87" hidden="1">
+    <row r="138" spans="1:87">
       <c r="A138" s="4">
         <v>137</v>
       </c>
@@ -20061,7 +20062,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="139" spans="1:87" hidden="1">
+    <row r="139" spans="1:87">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -20212,7 +20213,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="140" spans="1:87" hidden="1">
+    <row r="140" spans="1:87">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -20362,7 +20363,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="141" spans="1:87" ht="28.8" hidden="1">
+    <row r="141" spans="1:87" ht="28.8">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -20520,7 +20521,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="142" spans="1:87" ht="28.8" hidden="1">
+    <row r="142" spans="1:87" ht="28.8">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -20660,7 +20661,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="143" spans="1:87" hidden="1">
+    <row r="143" spans="1:87">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -20811,7 +20812,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="144" spans="1:87" hidden="1">
+    <row r="144" spans="1:87">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -20974,7 +20975,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="145" spans="1:87" ht="28.8" hidden="1">
+    <row r="145" spans="1:87" ht="28.8">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -21149,7 +21150,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="146" spans="1:87" ht="28.8" hidden="1">
+    <row r="146" spans="1:87" ht="28.8">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -21312,7 +21313,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="147" spans="1:87" hidden="1">
+    <row r="147" spans="1:87">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -21472,7 +21473,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="148" spans="1:87" hidden="1">
+    <row r="148" spans="1:87">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -21602,7 +21603,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="149" spans="1:87" ht="28.8" hidden="1">
+    <row r="149" spans="1:87" ht="28.8">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -21754,7 +21755,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="150" spans="1:87" hidden="1">
+    <row r="150" spans="1:87">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -21906,7 +21907,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="151" spans="1:87" ht="28.8" hidden="1">
+    <row r="151" spans="1:87" ht="28.8">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -22072,7 +22073,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="152" spans="1:87" hidden="1">
+    <row r="152" spans="1:87">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -22087,7 +22088,7 @@
       </c>
       <c r="E152" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F152" s="1">
         <f t="shared" si="9"/>
@@ -22221,7 +22222,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="153" spans="1:87" hidden="1">
+    <row r="153" spans="1:87">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -22367,7 +22368,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="154" spans="1:87" hidden="1">
+    <row r="154" spans="1:87">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -22486,7 +22487,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="155" spans="1:87" hidden="1">
+    <row r="155" spans="1:87">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -22630,7 +22631,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="156" spans="1:87" hidden="1">
+    <row r="156" spans="1:87">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -22771,7 +22772,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="157" spans="1:87" hidden="1">
+    <row r="157" spans="1:87">
       <c r="A157" s="4">
         <v>156</v>
       </c>
@@ -22915,7 +22916,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="158" spans="1:87" hidden="1">
+    <row r="158" spans="1:87">
       <c r="A158" s="4">
         <v>157</v>
       </c>
@@ -22966,7 +22967,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="159" spans="1:87" hidden="1">
+    <row r="159" spans="1:87">
       <c r="A159" s="4">
         <v>158</v>
       </c>
@@ -23145,7 +23146,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="160" spans="1:87" hidden="1">
+    <row r="160" spans="1:87">
       <c r="A160" s="4">
         <v>159</v>
       </c>
@@ -23238,7 +23239,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="161" spans="1:87" hidden="1">
+    <row r="161" spans="1:87">
       <c r="A161" s="4">
         <v>160</v>
       </c>
@@ -23388,7 +23389,7 @@
       <c r="BU161" s="167"/>
       <c r="CE161" s="167"/>
     </row>
-    <row r="162" spans="1:87" hidden="1">
+    <row r="162" spans="1:87">
       <c r="A162" s="4">
         <v>161</v>
       </c>
@@ -23463,7 +23464,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="163" spans="1:87" hidden="1">
+    <row r="163" spans="1:87">
       <c r="A163" s="4">
         <v>162</v>
       </c>
@@ -23478,7 +23479,7 @@
       </c>
       <c r="E163" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F163" s="1">
         <f t="shared" si="11"/>
@@ -23533,7 +23534,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="164" spans="1:87" hidden="1">
+    <row r="164" spans="1:87">
       <c r="A164" s="4">
         <v>163</v>
       </c>
@@ -23676,7 +23677,7 @@
       <c r="BU164" s="167"/>
       <c r="CE164" s="167"/>
     </row>
-    <row r="165" spans="1:87" ht="57.6" hidden="1">
+    <row r="165" spans="1:87" ht="57.6">
       <c r="A165" s="4">
         <v>164</v>
       </c>
@@ -23809,7 +23810,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="166" spans="1:87" hidden="1">
+    <row r="166" spans="1:87">
       <c r="A166" s="4">
         <v>165</v>
       </c>
@@ -23887,7 +23888,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="167" spans="1:87" hidden="1">
+    <row r="167" spans="1:87">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -23963,7 +23964,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="168" spans="1:87" hidden="1">
+    <row r="168" spans="1:87">
       <c r="A168" s="4">
         <v>167</v>
       </c>
@@ -24106,7 +24107,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="169" spans="1:87" hidden="1">
+    <row r="169" spans="1:87">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -24151,7 +24152,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="170" spans="1:87" hidden="1">
+    <row r="170" spans="1:87">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -24286,7 +24287,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="171" spans="1:87" hidden="1">
+    <row r="171" spans="1:87">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -24385,7 +24386,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="172" spans="1:87" hidden="1">
+    <row r="172" spans="1:87">
       <c r="A172" s="4">
         <v>171</v>
       </c>
@@ -24528,7 +24529,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="173" spans="1:87" ht="43.2" hidden="1">
+    <row r="173" spans="1:87" ht="43.2">
       <c r="A173" s="4">
         <v>172</v>
       </c>
@@ -24670,7 +24671,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="174" spans="1:87" hidden="1">
+    <row r="174" spans="1:87">
       <c r="A174" s="4">
         <v>173</v>
       </c>
@@ -24805,7 +24806,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="175" spans="1:87" hidden="1">
+    <row r="175" spans="1:87">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -24906,7 +24907,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="176" spans="1:87" ht="43.2" hidden="1">
+    <row r="176" spans="1:87" ht="43.2">
       <c r="A176" s="4">
         <v>175</v>
       </c>
@@ -25046,7 +25047,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="177" spans="1:87" hidden="1">
+    <row r="177" spans="1:87">
       <c r="A177" s="4">
         <v>176</v>
       </c>
@@ -25186,7 +25187,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="178" spans="1:87" hidden="1">
+    <row r="178" spans="1:87">
       <c r="A178" s="4">
         <v>177</v>
       </c>
@@ -25321,7 +25322,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="179" spans="1:87" hidden="1">
+    <row r="179" spans="1:87">
       <c r="A179" s="4">
         <v>178</v>
       </c>
@@ -25413,7 +25414,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="180" spans="1:87" hidden="1">
+    <row r="180" spans="1:87">
       <c r="A180" s="4">
         <v>179</v>
       </c>
@@ -25519,7 +25520,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="181" spans="1:87" hidden="1">
+    <row r="181" spans="1:87">
       <c r="A181" s="4">
         <v>180</v>
       </c>
@@ -25636,7 +25637,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="182" spans="1:87" hidden="1">
+    <row r="182" spans="1:87">
       <c r="A182" s="4">
         <v>181</v>
       </c>
@@ -25785,7 +25786,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="183" spans="1:87" hidden="1">
+    <row r="183" spans="1:87">
       <c r="A183" s="4">
         <v>182</v>
       </c>
@@ -25947,7 +25948,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="184" spans="1:87" hidden="1">
+    <row r="184" spans="1:87">
       <c r="A184" s="4">
         <v>183</v>
       </c>
@@ -26084,7 +26085,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="185" spans="1:87" hidden="1">
+    <row r="185" spans="1:87">
       <c r="A185" s="4">
         <v>184</v>
       </c>
@@ -26219,7 +26220,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="186" spans="1:87" hidden="1">
+    <row r="186" spans="1:87">
       <c r="A186" s="4">
         <v>185</v>
       </c>
@@ -26352,7 +26353,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="187" spans="1:87" hidden="1">
+    <row r="187" spans="1:87">
       <c r="A187" s="4">
         <v>186</v>
       </c>
@@ -26490,7 +26491,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="188" spans="1:87" hidden="1">
+    <row r="188" spans="1:87">
       <c r="A188" s="4">
         <v>187</v>
       </c>
@@ -26568,7 +26569,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="189" spans="1:87" hidden="1">
+    <row r="189" spans="1:87">
       <c r="A189" s="4">
         <v>188</v>
       </c>
@@ -26705,7 +26706,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="190" spans="1:87" hidden="1">
+    <row r="190" spans="1:87">
       <c r="A190" s="4">
         <v>189</v>
       </c>
@@ -26843,7 +26844,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="191" spans="1:87" hidden="1">
+    <row r="191" spans="1:87">
       <c r="A191" s="4">
         <v>190</v>
       </c>
@@ -26972,7 +26973,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="192" spans="1:87" hidden="1">
+    <row r="192" spans="1:87">
       <c r="A192" s="4">
         <v>191</v>
       </c>
@@ -27112,7 +27113,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="193" spans="1:87" hidden="1">
+    <row r="193" spans="1:87">
       <c r="A193" s="4">
         <v>192</v>
       </c>
@@ -27246,7 +27247,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="194" spans="1:87" hidden="1">
+    <row r="194" spans="1:87">
       <c r="A194" s="4">
         <v>193</v>
       </c>
@@ -27367,7 +27368,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="195" spans="1:87" hidden="1">
+    <row r="195" spans="1:87">
       <c r="A195" s="4">
         <v>194</v>
       </c>
@@ -27503,7 +27504,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="196" spans="1:87" hidden="1">
+    <row r="196" spans="1:87">
       <c r="A196" s="4">
         <v>195</v>
       </c>
@@ -27638,7 +27639,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="197" spans="1:87" hidden="1">
+    <row r="197" spans="1:87">
       <c r="A197" s="4">
         <v>196</v>
       </c>
@@ -27771,7 +27772,7 @@
       <c r="BU197" s="167"/>
       <c r="CE197" s="167"/>
     </row>
-    <row r="198" spans="1:87" hidden="1">
+    <row r="198" spans="1:87">
       <c r="A198" s="4">
         <v>197</v>
       </c>
@@ -27913,7 +27914,7 @@
       <c r="BU198" s="167"/>
       <c r="CE198" s="167"/>
     </row>
-    <row r="199" spans="1:87" hidden="1">
+    <row r="199" spans="1:87">
       <c r="A199" s="4">
         <v>198</v>
       </c>
@@ -28028,7 +28029,7 @@
       <c r="BU199" s="167"/>
       <c r="CE199" s="167"/>
     </row>
-    <row r="200" spans="1:87" hidden="1">
+    <row r="200" spans="1:87">
       <c r="A200" s="4">
         <v>199</v>
       </c>
@@ -28099,7 +28100,7 @@
       <c r="BU200" s="167"/>
       <c r="CE200" s="167"/>
     </row>
-    <row r="201" spans="1:87" hidden="1">
+    <row r="201" spans="1:87">
       <c r="A201" s="4">
         <v>200</v>
       </c>
@@ -28140,7 +28141,7 @@
       <c r="BU201" s="167"/>
       <c r="CE201" s="167"/>
     </row>
-    <row r="202" spans="1:87" ht="28.8" hidden="1">
+    <row r="202" spans="1:87" ht="28.8">
       <c r="A202" s="4">
         <v>201</v>
       </c>
@@ -28302,7 +28303,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="203" spans="1:87" hidden="1">
+    <row r="203" spans="1:87">
       <c r="A203" s="4">
         <v>202</v>
       </c>
@@ -28438,7 +28439,7 @@
       <c r="BU203" s="167"/>
       <c r="CE203" s="167"/>
     </row>
-    <row r="204" spans="1:87" hidden="1">
+    <row r="204" spans="1:87">
       <c r="A204" s="4">
         <v>203</v>
       </c>
@@ -28485,7 +28486,7 @@
       <c r="BU204" s="167"/>
       <c r="CE204" s="167"/>
     </row>
-    <row r="205" spans="1:87" hidden="1">
+    <row r="205" spans="1:87">
       <c r="A205" s="4">
         <v>204</v>
       </c>
@@ -28518,7 +28519,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="206" spans="1:87" hidden="1">
+    <row r="206" spans="1:87">
       <c r="A206" s="4">
         <v>205</v>
       </c>
@@ -28559,7 +28560,7 @@
       <c r="BU206" s="167"/>
       <c r="CE206" s="167"/>
     </row>
-    <row r="207" spans="1:87" hidden="1">
+    <row r="207" spans="1:87">
       <c r="A207" s="4">
         <v>206</v>
       </c>
@@ -28606,7 +28607,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="208" spans="1:87" hidden="1">
+    <row r="208" spans="1:87">
       <c r="A208" s="4">
         <v>207</v>
       </c>
@@ -28653,7 +28654,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="209" spans="1:87" hidden="1">
+    <row r="209" spans="1:87">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -28697,7 +28698,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="210" spans="1:87" hidden="1">
+    <row r="210" spans="1:87">
       <c r="A210" s="4">
         <v>209</v>
       </c>
@@ -28741,7 +28742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:87" hidden="1">
+    <row r="211" spans="1:87">
       <c r="A211" s="4">
         <v>210</v>
       </c>
@@ -28782,7 +28783,7 @@
       <c r="BU211" s="167"/>
       <c r="CE211" s="167"/>
     </row>
-    <row r="212" spans="1:87" hidden="1">
+    <row r="212" spans="1:87">
       <c r="A212" s="4">
         <v>211</v>
       </c>
@@ -28924,7 +28925,7 @@
       <c r="BU212" s="167"/>
       <c r="CE212" s="167"/>
     </row>
-    <row r="213" spans="1:87" hidden="1">
+    <row r="213" spans="1:87">
       <c r="A213" s="4">
         <v>212</v>
       </c>
@@ -29048,7 +29049,7 @@
       </c>
       <c r="AW213" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX213" s="1" t="s">
         <v>445</v>
@@ -29081,7 +29082,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="214" spans="1:87" hidden="1">
+    <row r="214" spans="1:87">
       <c r="A214" s="4">
         <v>213</v>
       </c>
@@ -29122,7 +29123,7 @@
       <c r="BU214" s="167"/>
       <c r="CE214" s="167"/>
     </row>
-    <row r="215" spans="1:87" hidden="1">
+    <row r="215" spans="1:87">
       <c r="A215" s="4">
         <v>214</v>
       </c>
@@ -29208,7 +29209,7 @@
       <c r="BU215" s="167"/>
       <c r="CE215" s="167"/>
     </row>
-    <row r="216" spans="1:87" hidden="1">
+    <row r="216" spans="1:87">
       <c r="A216" s="4">
         <v>215</v>
       </c>
@@ -29312,7 +29313,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="217" spans="1:87" hidden="1">
+    <row r="217" spans="1:87">
       <c r="A217" s="4">
         <v>216</v>
       </c>
@@ -29387,7 +29388,7 @@
       </c>
       <c r="BA217" s="184"/>
     </row>
-    <row r="218" spans="1:87" hidden="1">
+    <row r="218" spans="1:87">
       <c r="A218" s="4">
         <v>217</v>
       </c>
@@ -29520,7 +29521,7 @@
       <c r="BU218" s="167"/>
       <c r="CE218" s="167"/>
     </row>
-    <row r="219" spans="1:87" hidden="1">
+    <row r="219" spans="1:87">
       <c r="A219" s="4">
         <v>218</v>
       </c>
@@ -29653,7 +29654,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="220" spans="1:87" hidden="1">
+    <row r="220" spans="1:87">
       <c r="A220" s="4">
         <v>219</v>
       </c>
@@ -29694,7 +29695,7 @@
       <c r="BU220" s="167"/>
       <c r="CE220" s="167"/>
     </row>
-    <row r="221" spans="1:87" hidden="1">
+    <row r="221" spans="1:87">
       <c r="A221" s="4">
         <v>220</v>
       </c>
@@ -29738,7 +29739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:87" hidden="1">
+    <row r="222" spans="1:87">
       <c r="A222" s="4">
         <v>221</v>
       </c>
@@ -29782,7 +29783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:87" hidden="1">
+    <row r="223" spans="1:87">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -29826,7 +29827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:87" ht="28.8" hidden="1">
+    <row r="224" spans="1:87" ht="28.8">
       <c r="A224" s="4">
         <v>223</v>
       </c>
@@ -29950,7 +29951,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="225" spans="1:87" hidden="1">
+    <row r="225" spans="1:87">
       <c r="A225" s="4">
         <v>224</v>
       </c>
@@ -29987,7 +29988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:87" hidden="1">
+    <row r="226" spans="1:87">
       <c r="A226" s="4">
         <v>225</v>
       </c>
@@ -30081,7 +30082,7 @@
       <c r="BU226" s="167"/>
       <c r="CE226" s="167"/>
     </row>
-    <row r="227" spans="1:87" hidden="1">
+    <row r="227" spans="1:87">
       <c r="A227" s="4">
         <v>226</v>
       </c>
@@ -30148,7 +30149,7 @@
       <c r="BU227" s="167"/>
       <c r="CE227" s="167"/>
     </row>
-    <row r="228" spans="1:87" hidden="1">
+    <row r="228" spans="1:87">
       <c r="A228" s="4">
         <v>227</v>
       </c>
@@ -30185,7 +30186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:87" hidden="1">
+    <row r="229" spans="1:87">
       <c r="A229" s="4">
         <v>228</v>
       </c>
@@ -30277,7 +30278,7 @@
       <c r="BU229" s="167"/>
       <c r="CE229" s="167"/>
     </row>
-    <row r="230" spans="1:87" hidden="1">
+    <row r="230" spans="1:87">
       <c r="A230" s="4">
         <v>229</v>
       </c>
@@ -30377,7 +30378,7 @@
       <c r="BU230" s="167"/>
       <c r="CE230" s="167"/>
     </row>
-    <row r="231" spans="1:87" hidden="1">
+    <row r="231" spans="1:87">
       <c r="A231" s="4">
         <v>230</v>
       </c>
@@ -30454,7 +30455,7 @@
       <c r="BU231" s="167"/>
       <c r="CE231" s="167"/>
     </row>
-    <row r="232" spans="1:87" hidden="1">
+    <row r="232" spans="1:87">
       <c r="A232" s="4">
         <v>231</v>
       </c>
@@ -30540,7 +30541,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="233" spans="1:87" hidden="1">
+    <row r="233" spans="1:87">
       <c r="A233" s="4">
         <v>232</v>
       </c>
@@ -30641,7 +30642,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="234" spans="1:87" hidden="1">
+    <row r="234" spans="1:87">
       <c r="A234" s="4">
         <v>233</v>
       </c>
@@ -30748,7 +30749,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="235" spans="1:87" hidden="1">
+    <row r="235" spans="1:87">
       <c r="A235" s="4">
         <v>234</v>
       </c>
@@ -30912,7 +30913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:87" hidden="1">
+    <row r="236" spans="1:87">
       <c r="A236" s="4">
         <v>235</v>
       </c>
@@ -31012,7 +31013,7 @@
       <c r="BU236" s="167"/>
       <c r="CE236" s="167"/>
     </row>
-    <row r="237" spans="1:87" hidden="1">
+    <row r="237" spans="1:87">
       <c r="A237" s="4">
         <v>236</v>
       </c>
@@ -31041,7 +31042,7 @@
       </c>
       <c r="BA237" s="184"/>
     </row>
-    <row r="238" spans="1:87" hidden="1">
+    <row r="238" spans="1:87">
       <c r="A238" s="4">
         <v>237</v>
       </c>
@@ -31142,7 +31143,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="239" spans="1:87" hidden="1">
+    <row r="239" spans="1:87">
       <c r="A239" s="4">
         <v>238</v>
       </c>
@@ -31271,7 +31272,7 @@
       <c r="BU239" s="167"/>
       <c r="CE239" s="167"/>
     </row>
-    <row r="240" spans="1:87" hidden="1">
+    <row r="240" spans="1:87">
       <c r="A240" s="4">
         <v>239</v>
       </c>
@@ -31517,7 +31518,7 @@
       </c>
       <c r="E242" s="1">
         <f t="shared" ca="1" si="15"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F242" s="1">
         <f t="shared" si="17"/>
@@ -31906,7 +31907,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="246" spans="1:88" ht="28.8" hidden="1">
+    <row r="246" spans="1:88" ht="28.8">
       <c r="A246" s="4">
         <v>245</v>
       </c>
@@ -32049,7 +32050,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="247" spans="1:88" ht="28.8" hidden="1">
+    <row r="247" spans="1:88" ht="28.8">
       <c r="A247" s="4">
         <v>246</v>
       </c>
@@ -32168,7 +32169,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="248" spans="1:88" hidden="1">
+    <row r="248" spans="1:88">
       <c r="A248" s="4">
         <v>247</v>
       </c>
@@ -32265,7 +32266,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="249" spans="1:88" hidden="1">
+    <row r="249" spans="1:88">
       <c r="A249" s="4">
         <v>248</v>
       </c>
@@ -32363,7 +32364,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="250" spans="1:88" hidden="1">
+    <row r="250" spans="1:88">
       <c r="A250" s="4">
         <v>249</v>
       </c>
@@ -32461,7 +32462,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="251" spans="1:88" ht="28.8" hidden="1">
+    <row r="251" spans="1:88" ht="28.8">
       <c r="A251" s="4">
         <v>250</v>
       </c>
@@ -32584,7 +32585,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="252" spans="1:88" ht="28.8" hidden="1">
+    <row r="252" spans="1:88" ht="28.8">
       <c r="A252" s="4">
         <v>251</v>
       </c>
@@ -32673,7 +32674,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="253" spans="1:88" hidden="1">
+    <row r="253" spans="1:88">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -32763,7 +32764,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="254" spans="1:88" hidden="1">
+    <row r="254" spans="1:88">
       <c r="A254" s="4">
         <v>253</v>
       </c>
@@ -32807,7 +32808,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="255" spans="1:88" hidden="1">
+    <row r="255" spans="1:88">
       <c r="A255" s="4">
         <v>254</v>
       </c>
@@ -32911,7 +32912,7 @@
       </c>
       <c r="AW255" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX255" s="1" t="s">
         <v>445</v>
@@ -32927,7 +32928,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="256" spans="1:88" ht="28.8" hidden="1">
+    <row r="256" spans="1:88" ht="28.8">
       <c r="A256" s="4">
         <v>255</v>
       </c>
@@ -33053,7 +33054,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="257" spans="1:88" hidden="1">
+    <row r="257" spans="1:88">
       <c r="A257" s="4">
         <v>256</v>
       </c>
@@ -33178,7 +33179,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="258" spans="1:88" hidden="1">
+    <row r="258" spans="1:88">
       <c r="A258" s="4">
         <v>257</v>
       </c>
@@ -33211,7 +33212,7 @@
       </c>
       <c r="BA258" s="184"/>
     </row>
-    <row r="259" spans="1:88" hidden="1">
+    <row r="259" spans="1:88">
       <c r="A259" s="4">
         <v>258</v>
       </c>
@@ -33244,7 +33245,7 @@
       </c>
       <c r="BA259" s="184"/>
     </row>
-    <row r="260" spans="1:88" hidden="1">
+    <row r="260" spans="1:88">
       <c r="A260" s="4">
         <v>259</v>
       </c>
@@ -33372,7 +33373,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="261" spans="1:88" hidden="1">
+    <row r="261" spans="1:88">
       <c r="A261" s="4">
         <v>260</v>
       </c>
@@ -33429,7 +33430,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="262" spans="1:88" hidden="1">
+    <row r="262" spans="1:88">
       <c r="A262" s="4">
         <v>261</v>
       </c>
@@ -33539,7 +33540,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="263" spans="1:88" hidden="1">
+    <row r="263" spans="1:88">
       <c r="A263" s="4">
         <v>262</v>
       </c>
@@ -33652,7 +33653,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="264" spans="1:88" hidden="1">
+    <row r="264" spans="1:88">
       <c r="A264" s="4">
         <v>263</v>
       </c>
@@ -33667,7 +33668,7 @@
       </c>
       <c r="E264" s="1">
         <f t="shared" ca="1" si="18"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F264" s="1">
         <f t="shared" si="19"/>
@@ -33810,7 +33811,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="265" spans="1:88" hidden="1">
+    <row r="265" spans="1:88">
       <c r="A265" s="4">
         <v>264</v>
       </c>
@@ -33914,7 +33915,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="266" spans="1:88" hidden="1">
+    <row r="266" spans="1:88">
       <c r="A266" s="4">
         <v>265</v>
       </c>
@@ -34003,7 +34004,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="267" spans="1:88" hidden="1">
+    <row r="267" spans="1:88">
       <c r="A267" s="4">
         <v>266</v>
       </c>
@@ -34113,7 +34114,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="268" spans="1:88" hidden="1">
+    <row r="268" spans="1:88">
       <c r="A268" s="4">
         <v>267</v>
       </c>
@@ -34259,7 +34260,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="269" spans="1:88" hidden="1">
+    <row r="269" spans="1:88">
       <c r="A269" s="4">
         <v>268</v>
       </c>
@@ -34378,7 +34379,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="270" spans="1:88" hidden="1">
+    <row r="270" spans="1:88">
       <c r="A270" s="4">
         <v>269</v>
       </c>
@@ -34506,7 +34507,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="271" spans="1:88" ht="28.8" hidden="1">
+    <row r="271" spans="1:88" ht="28.8">
       <c r="A271" s="4">
         <v>270</v>
       </c>
@@ -34628,7 +34629,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="272" spans="1:88" hidden="1">
+    <row r="272" spans="1:88">
       <c r="A272" s="4">
         <v>271</v>
       </c>
@@ -34679,7 +34680,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="273" spans="1:107" hidden="1">
+    <row r="273" spans="1:107">
       <c r="A273" s="4">
         <v>272</v>
       </c>
@@ -34810,7 +34811,7 @@
       <c r="DB273" s="170"/>
       <c r="DC273" s="170"/>
     </row>
-    <row r="274" spans="1:107" hidden="1">
+    <row r="274" spans="1:107">
       <c r="A274" s="4">
         <v>273</v>
       </c>
@@ -34957,7 +34958,7 @@
       <c r="DB274" s="170"/>
       <c r="DC274" s="170"/>
     </row>
-    <row r="275" spans="1:107" hidden="1">
+    <row r="275" spans="1:107">
       <c r="A275" s="4">
         <v>274</v>
       </c>
@@ -35018,7 +35019,7 @@
       <c r="DB275" s="170"/>
       <c r="DC275" s="170"/>
     </row>
-    <row r="276" spans="1:107" hidden="1">
+    <row r="276" spans="1:107">
       <c r="A276" s="4">
         <v>275</v>
       </c>
@@ -35084,7 +35085,7 @@
       <c r="DB276" s="170"/>
       <c r="DC276" s="170"/>
     </row>
-    <row r="277" spans="1:107" hidden="1">
+    <row r="277" spans="1:107">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -35193,7 +35194,7 @@
       <c r="DB277" s="170"/>
       <c r="DC277" s="170"/>
     </row>
-    <row r="278" spans="1:107" hidden="1">
+    <row r="278" spans="1:107">
       <c r="A278" s="4">
         <v>277</v>
       </c>
@@ -35315,7 +35316,7 @@
       </c>
       <c r="AW278" s="1">
         <f t="shared" ca="1" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX278" s="1" t="s">
         <v>445</v>
@@ -35346,7 +35347,7 @@
       <c r="DB278" s="170"/>
       <c r="DC278" s="170"/>
     </row>
-    <row r="279" spans="1:107" ht="28.8" hidden="1">
+    <row r="279" spans="1:107" ht="28.8">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -35457,7 +35458,7 @@
       <c r="DB279" s="170"/>
       <c r="DC279" s="170"/>
     </row>
-    <row r="280" spans="1:107" hidden="1">
+    <row r="280" spans="1:107">
       <c r="A280" s="4">
         <v>279</v>
       </c>
@@ -35563,7 +35564,7 @@
       <c r="DB280" s="170"/>
       <c r="DC280" s="170"/>
     </row>
-    <row r="281" spans="1:107" hidden="1">
+    <row r="281" spans="1:107">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -35704,7 +35705,7 @@
       <c r="DB281" s="170"/>
       <c r="DC281" s="170"/>
     </row>
-    <row r="282" spans="1:107" hidden="1">
+    <row r="282" spans="1:107">
       <c r="A282" s="4">
         <v>281</v>
       </c>
@@ -35768,7 +35769,7 @@
       <c r="DB282" s="170"/>
       <c r="DC282" s="170"/>
     </row>
-    <row r="283" spans="1:107" hidden="1">
+    <row r="283" spans="1:107">
       <c r="A283" s="4">
         <v>282</v>
       </c>
@@ -35916,7 +35917,7 @@
       <c r="DB283" s="170"/>
       <c r="DC283" s="170"/>
     </row>
-    <row r="284" spans="1:107" hidden="1">
+    <row r="284" spans="1:107">
       <c r="A284" s="4">
         <v>283</v>
       </c>
@@ -36024,7 +36025,7 @@
       <c r="DB284" s="170"/>
       <c r="DC284" s="170"/>
     </row>
-    <row r="285" spans="1:107" hidden="1">
+    <row r="285" spans="1:107">
       <c r="A285" s="4">
         <v>284</v>
       </c>
@@ -36127,7 +36128,7 @@
       <c r="DB285" s="170"/>
       <c r="DC285" s="170"/>
     </row>
-    <row r="286" spans="1:107" ht="28.8" hidden="1">
+    <row r="286" spans="1:107" ht="28.8">
       <c r="A286" s="4">
         <v>285</v>
       </c>
@@ -36207,7 +36208,7 @@
       </c>
       <c r="AW286" s="1">
         <f t="shared" ca="1" si="20"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX286" s="1" t="s">
         <v>63</v>
@@ -36238,7 +36239,7 @@
       <c r="DB286" s="170"/>
       <c r="DC286" s="170"/>
     </row>
-    <row r="287" spans="1:107" hidden="1">
+    <row r="287" spans="1:107">
       <c r="A287" s="4">
         <v>286</v>
       </c>
@@ -36349,7 +36350,7 @@
       <c r="DB287" s="170"/>
       <c r="DC287" s="170"/>
     </row>
-    <row r="288" spans="1:107" hidden="1">
+    <row r="288" spans="1:107">
       <c r="A288" s="4">
         <v>287</v>
       </c>
@@ -36422,7 +36423,7 @@
       <c r="DB288" s="170"/>
       <c r="DC288" s="170"/>
     </row>
-    <row r="289" spans="1:107" ht="28.8" hidden="1">
+    <row r="289" spans="1:107" ht="28.8">
       <c r="A289" s="4">
         <v>288</v>
       </c>
@@ -36531,7 +36532,7 @@
       <c r="DB289" s="170"/>
       <c r="DC289" s="170"/>
     </row>
-    <row r="290" spans="1:107" hidden="1">
+    <row r="290" spans="1:107">
       <c r="A290" s="4">
         <v>289</v>
       </c>
@@ -36666,7 +36667,7 @@
       <c r="DB290" s="170"/>
       <c r="DC290" s="170"/>
     </row>
-    <row r="291" spans="1:107" hidden="1">
+    <row r="291" spans="1:107">
       <c r="A291" s="4">
         <v>290</v>
       </c>
@@ -36718,7 +36719,7 @@
       <c r="DB291" s="170"/>
       <c r="DC291" s="170"/>
     </row>
-    <row r="292" spans="1:107" hidden="1">
+    <row r="292" spans="1:107">
       <c r="A292" s="4">
         <v>291</v>
       </c>
@@ -36865,7 +36866,7 @@
       <c r="DB292" s="170"/>
       <c r="DC292" s="170"/>
     </row>
-    <row r="293" spans="1:107" hidden="1">
+    <row r="293" spans="1:107">
       <c r="A293" s="4">
         <v>292</v>
       </c>
@@ -37009,7 +37010,7 @@
       <c r="DB293" s="170"/>
       <c r="DC293" s="170"/>
     </row>
-    <row r="294" spans="1:107" hidden="1">
+    <row r="294" spans="1:107">
       <c r="A294" s="4">
         <v>293</v>
       </c>
@@ -37058,7 +37059,7 @@
       <c r="DB294" s="170"/>
       <c r="DC294" s="170"/>
     </row>
-    <row r="295" spans="1:107" hidden="1">
+    <row r="295" spans="1:107">
       <c r="A295" s="4">
         <v>294</v>
       </c>
@@ -37084,7 +37085,7 @@
       </c>
       <c r="AW295" s="1">
         <f t="shared" ca="1" si="20"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX295" s="1" t="s">
         <v>63</v>
@@ -37094,7 +37095,7 @@
       </c>
       <c r="BA295" s="184"/>
     </row>
-    <row r="296" spans="1:107" hidden="1">
+    <row r="296" spans="1:107">
       <c r="A296" s="4">
         <v>295</v>
       </c>
@@ -37133,7 +37134,7 @@
       </c>
       <c r="BA296" s="203"/>
     </row>
-    <row r="297" spans="1:107" hidden="1">
+    <row r="297" spans="1:107">
       <c r="A297" s="4">
         <v>296</v>
       </c>
@@ -37169,7 +37170,7 @@
       </c>
       <c r="BA297" s="184"/>
     </row>
-    <row r="298" spans="1:107" hidden="1">
+    <row r="298" spans="1:107">
       <c r="A298" s="4">
         <v>297</v>
       </c>
@@ -37205,7 +37206,7 @@
       </c>
       <c r="BA298" s="184"/>
     </row>
-    <row r="299" spans="1:107" hidden="1">
+    <row r="299" spans="1:107">
       <c r="A299" s="4">
         <v>298</v>
       </c>
@@ -37241,7 +37242,7 @@
       </c>
       <c r="BA299" s="184"/>
     </row>
-    <row r="300" spans="1:107" hidden="1">
+    <row r="300" spans="1:107">
       <c r="A300" s="4">
         <v>299</v>
       </c>
@@ -37280,7 +37281,7 @@
       </c>
       <c r="BA300" s="184"/>
     </row>
-    <row r="301" spans="1:107" hidden="1">
+    <row r="301" spans="1:107">
       <c r="A301" s="4">
         <v>300</v>
       </c>
@@ -37316,7 +37317,7 @@
       </c>
       <c r="BA301" s="184"/>
     </row>
-    <row r="302" spans="1:107" hidden="1">
+    <row r="302" spans="1:107">
       <c r="A302" s="4">
         <v>301</v>
       </c>
@@ -37352,7 +37353,7 @@
       </c>
       <c r="BA302" s="184"/>
     </row>
-    <row r="303" spans="1:107" hidden="1">
+    <row r="303" spans="1:107">
       <c r="A303" s="4">
         <v>302</v>
       </c>
@@ -37385,7 +37386,7 @@
       </c>
       <c r="BA303" s="184"/>
     </row>
-    <row r="304" spans="1:107" hidden="1">
+    <row r="304" spans="1:107">
       <c r="A304" s="4">
         <v>303</v>
       </c>
@@ -37424,7 +37425,7 @@
       </c>
       <c r="BA304" s="184"/>
     </row>
-    <row r="305" spans="1:53" hidden="1">
+    <row r="305" spans="1:53">
       <c r="A305" s="4">
         <v>304</v>
       </c>
@@ -37460,7 +37461,7 @@
       </c>
       <c r="BA305" s="184"/>
     </row>
-    <row r="306" spans="1:53" hidden="1">
+    <row r="306" spans="1:53">
       <c r="A306" s="4">
         <v>305</v>
       </c>
@@ -37493,7 +37494,7 @@
       </c>
       <c r="BA306" s="184"/>
     </row>
-    <row r="307" spans="1:53" hidden="1">
+    <row r="307" spans="1:53">
       <c r="A307" s="4">
         <v>306</v>
       </c>
@@ -37526,7 +37527,7 @@
       </c>
       <c r="BA307" s="184"/>
     </row>
-    <row r="308" spans="1:53" hidden="1">
+    <row r="308" spans="1:53">
       <c r="A308" s="4">
         <v>307</v>
       </c>
@@ -37559,7 +37560,7 @@
       </c>
       <c r="BA308" s="184"/>
     </row>
-    <row r="309" spans="1:53" hidden="1">
+    <row r="309" spans="1:53">
       <c r="A309" s="4">
         <v>308</v>
       </c>
@@ -37592,7 +37593,7 @@
       </c>
       <c r="BA309" s="184"/>
     </row>
-    <row r="310" spans="1:53" hidden="1">
+    <row r="310" spans="1:53">
       <c r="A310" s="4">
         <v>309</v>
       </c>
@@ -37625,7 +37626,7 @@
       </c>
       <c r="BA310" s="184"/>
     </row>
-    <row r="311" spans="1:53" hidden="1">
+    <row r="311" spans="1:53">
       <c r="A311" s="4">
         <v>310</v>
       </c>
@@ -37658,7 +37659,7 @@
       </c>
       <c r="BA311" s="184"/>
     </row>
-    <row r="312" spans="1:53" hidden="1">
+    <row r="312" spans="1:53">
       <c r="A312" s="4">
         <v>311</v>
       </c>
@@ -37684,14 +37685,14 @@
       </c>
       <c r="AW312" s="1">
         <f t="shared" ca="1" si="20"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX312" s="1" t="s">
         <v>63</v>
       </c>
       <c r="BA312" s="184"/>
     </row>
-    <row r="313" spans="1:53" hidden="1">
+    <row r="313" spans="1:53">
       <c r="A313" s="4">
         <v>312</v>
       </c>
@@ -37730,7 +37731,7 @@
       </c>
       <c r="BA313" s="184"/>
     </row>
-    <row r="314" spans="1:53" hidden="1">
+    <row r="314" spans="1:53">
       <c r="A314" s="4">
         <v>313</v>
       </c>
@@ -37763,7 +37764,7 @@
       </c>
       <c r="BA314" s="184"/>
     </row>
-    <row r="315" spans="1:53" hidden="1">
+    <row r="315" spans="1:53">
       <c r="A315" s="4">
         <v>314</v>
       </c>
@@ -37796,7 +37797,7 @@
       </c>
       <c r="BA315" s="184"/>
     </row>
-    <row r="316" spans="1:53" hidden="1">
+    <row r="316" spans="1:53">
       <c r="A316" s="4">
         <v>315</v>
       </c>
@@ -37829,7 +37830,7 @@
       </c>
       <c r="BA316" s="184"/>
     </row>
-    <row r="317" spans="1:53" hidden="1">
+    <row r="317" spans="1:53">
       <c r="A317" s="4">
         <v>316</v>
       </c>
@@ -37862,7 +37863,7 @@
       </c>
       <c r="BA317" s="184"/>
     </row>
-    <row r="318" spans="1:53" hidden="1">
+    <row r="318" spans="1:53">
       <c r="A318" s="4">
         <v>317</v>
       </c>
@@ -37901,7 +37902,7 @@
       </c>
       <c r="BA318" s="184"/>
     </row>
-    <row r="319" spans="1:53" hidden="1">
+    <row r="319" spans="1:53">
       <c r="A319" s="4">
         <v>318</v>
       </c>
@@ -37940,7 +37941,7 @@
       </c>
       <c r="BA319" s="184"/>
     </row>
-    <row r="320" spans="1:53" hidden="1">
+    <row r="320" spans="1:53">
       <c r="A320" s="4">
         <v>319</v>
       </c>
@@ -37976,7 +37977,7 @@
       </c>
       <c r="BA320" s="184"/>
     </row>
-    <row r="321" spans="1:53" hidden="1">
+    <row r="321" spans="1:53">
       <c r="A321" s="4">
         <v>320</v>
       </c>
@@ -38009,7 +38010,7 @@
       </c>
       <c r="BA321" s="184"/>
     </row>
-    <row r="322" spans="1:53" hidden="1">
+    <row r="322" spans="1:53">
       <c r="A322" s="4">
         <v>321</v>
       </c>
@@ -38045,7 +38046,7 @@
       </c>
       <c r="BA322" s="184"/>
     </row>
-    <row r="323" spans="1:53" hidden="1">
+    <row r="323" spans="1:53">
       <c r="A323" s="4">
         <v>322</v>
       </c>
@@ -38078,7 +38079,7 @@
       </c>
       <c r="BA323" s="184"/>
     </row>
-    <row r="324" spans="1:53" hidden="1">
+    <row r="324" spans="1:53">
       <c r="A324" s="4">
         <v>323</v>
       </c>
@@ -38111,7 +38112,7 @@
       </c>
       <c r="BA324" s="184"/>
     </row>
-    <row r="325" spans="1:53" hidden="1">
+    <row r="325" spans="1:53">
       <c r="A325" s="4">
         <v>324</v>
       </c>
@@ -38147,7 +38148,7 @@
       </c>
       <c r="BA325" s="184"/>
     </row>
-    <row r="326" spans="1:53" hidden="1">
+    <row r="326" spans="1:53">
       <c r="A326" s="4">
         <v>325</v>
       </c>
@@ -38180,7 +38181,7 @@
       </c>
       <c r="BA326" s="184"/>
     </row>
-    <row r="327" spans="1:53" hidden="1">
+    <row r="327" spans="1:53">
       <c r="A327" s="4">
         <v>326</v>
       </c>
@@ -38206,7 +38207,7 @@
       </c>
       <c r="AW327" s="1">
         <f t="shared" ca="1" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX327" s="1" t="s">
         <v>63</v>
@@ -38216,7 +38217,7 @@
       </c>
       <c r="BA327" s="184"/>
     </row>
-    <row r="328" spans="1:53" hidden="1">
+    <row r="328" spans="1:53">
       <c r="A328" s="4">
         <v>327</v>
       </c>
@@ -38249,7 +38250,7 @@
       </c>
       <c r="BA328" s="184"/>
     </row>
-    <row r="329" spans="1:53" hidden="1">
+    <row r="329" spans="1:53">
       <c r="A329" s="4">
         <v>328</v>
       </c>
@@ -38282,7 +38283,7 @@
       </c>
       <c r="BA329" s="184"/>
     </row>
-    <row r="330" spans="1:53" hidden="1">
+    <row r="330" spans="1:53">
       <c r="A330" s="4">
         <v>329</v>
       </c>
@@ -38315,7 +38316,7 @@
       </c>
       <c r="BA330" s="184"/>
     </row>
-    <row r="331" spans="1:53" hidden="1">
+    <row r="331" spans="1:53">
       <c r="A331" s="4">
         <v>330</v>
       </c>
@@ -38348,7 +38349,7 @@
       </c>
       <c r="BA331" s="184"/>
     </row>
-    <row r="332" spans="1:53" hidden="1">
+    <row r="332" spans="1:53">
       <c r="A332" s="4">
         <v>331</v>
       </c>
@@ -38384,7 +38385,7 @@
       </c>
       <c r="BA332" s="184"/>
     </row>
-    <row r="333" spans="1:53" hidden="1">
+    <row r="333" spans="1:53">
       <c r="A333" s="4">
         <v>332</v>
       </c>
@@ -38420,7 +38421,7 @@
       </c>
       <c r="BA333" s="184"/>
     </row>
-    <row r="334" spans="1:53" hidden="1">
+    <row r="334" spans="1:53">
       <c r="A334" s="4">
         <v>333</v>
       </c>
@@ -38453,7 +38454,7 @@
       </c>
       <c r="BA334" s="184"/>
     </row>
-    <row r="335" spans="1:53" hidden="1">
+    <row r="335" spans="1:53">
       <c r="A335" s="4">
         <v>334</v>
       </c>
@@ -38492,7 +38493,7 @@
       </c>
       <c r="BA335" s="184"/>
     </row>
-    <row r="336" spans="1:53" hidden="1">
+    <row r="336" spans="1:53">
       <c r="A336" s="4">
         <v>335</v>
       </c>
@@ -38531,7 +38532,7 @@
       </c>
       <c r="BA336" s="184"/>
     </row>
-    <row r="337" spans="1:87" hidden="1">
+    <row r="337" spans="1:87">
       <c r="A337" s="4">
         <v>336</v>
       </c>
@@ -38567,7 +38568,7 @@
       </c>
       <c r="BA337" s="184"/>
     </row>
-    <row r="338" spans="1:87" hidden="1">
+    <row r="338" spans="1:87">
       <c r="A338" s="4">
         <v>337</v>
       </c>
@@ -38600,7 +38601,7 @@
       </c>
       <c r="BA338" s="184"/>
     </row>
-    <row r="339" spans="1:87" hidden="1">
+    <row r="339" spans="1:87">
       <c r="A339" s="4">
         <v>338</v>
       </c>
@@ -38636,7 +38637,7 @@
       </c>
       <c r="BA339" s="184"/>
     </row>
-    <row r="340" spans="1:87" hidden="1">
+    <row r="340" spans="1:87">
       <c r="A340" s="4">
         <v>339</v>
       </c>
@@ -38675,7 +38676,7 @@
       </c>
       <c r="BA340" s="184"/>
     </row>
-    <row r="341" spans="1:87" hidden="1">
+    <row r="341" spans="1:87">
       <c r="A341" s="4">
         <v>340</v>
       </c>
@@ -38785,7 +38786,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="342" spans="1:87" hidden="1">
+    <row r="342" spans="1:87">
       <c r="A342" s="4">
         <v>341</v>
       </c>
@@ -38895,7 +38896,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="343" spans="1:87" hidden="1">
+    <row r="343" spans="1:87">
       <c r="A343" s="4">
         <v>342</v>
       </c>
@@ -38999,7 +39000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:87" hidden="1">
+    <row r="344" spans="1:87">
       <c r="A344" s="4">
         <v>343</v>
       </c>
@@ -39124,7 +39125,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="345" spans="1:87" hidden="1">
+    <row r="345" spans="1:87">
       <c r="A345" s="4">
         <v>344</v>
       </c>
@@ -39237,7 +39238,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="346" spans="1:87" hidden="1">
+    <row r="346" spans="1:87">
       <c r="A346" s="4">
         <v>345</v>
       </c>
@@ -39353,7 +39354,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="347" spans="1:87" hidden="1">
+    <row r="347" spans="1:87">
       <c r="A347" s="4">
         <v>346</v>
       </c>
@@ -39469,7 +39470,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="348" spans="1:87" hidden="1">
+    <row r="348" spans="1:87">
       <c r="A348" s="4">
         <v>347</v>
       </c>
@@ -39573,7 +39574,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="349" spans="1:87" hidden="1">
+    <row r="349" spans="1:87">
       <c r="A349" s="4">
         <v>348</v>
       </c>
@@ -39704,7 +39705,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="350" spans="1:87" hidden="1">
+    <row r="350" spans="1:87">
       <c r="A350" s="4">
         <v>349</v>
       </c>
@@ -39817,7 +39818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:87" hidden="1">
+    <row r="351" spans="1:87">
       <c r="A351" s="4">
         <v>350</v>
       </c>
@@ -39939,7 +39940,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="352" spans="1:87" hidden="1">
+    <row r="352" spans="1:87">
       <c r="A352" s="4">
         <v>351</v>
       </c>
@@ -40061,7 +40062,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="353" spans="1:87" hidden="1">
+    <row r="353" spans="1:87">
       <c r="A353" s="4">
         <v>352</v>
       </c>
@@ -40171,7 +40172,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="354" spans="1:87" hidden="1">
+    <row r="354" spans="1:87">
       <c r="A354" s="4">
         <v>353</v>
       </c>
@@ -40260,7 +40261,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="355" spans="1:87" ht="15.6" hidden="1">
+    <row r="355" spans="1:87" ht="15.6">
       <c r="A355" s="4">
         <v>354</v>
       </c>
@@ -40374,7 +40375,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="356" spans="1:87" ht="15.6" hidden="1">
+    <row r="356" spans="1:87" ht="15.6">
       <c r="A356" s="4">
         <v>355</v>
       </c>
@@ -40508,7 +40509,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="357" spans="1:87" hidden="1">
+    <row r="357" spans="1:87">
       <c r="A357" s="4">
         <v>356</v>
       </c>
@@ -40615,7 +40616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:87" ht="15.6" hidden="1">
+    <row r="358" spans="1:87" ht="15.6">
       <c r="A358" s="4">
         <v>357</v>
       </c>
@@ -40726,7 +40727,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="359" spans="1:87" hidden="1">
+    <row r="359" spans="1:87">
       <c r="A359" s="4">
         <v>358</v>
       </c>
@@ -40833,7 +40834,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="360" spans="1:87" ht="15.6" hidden="1">
+    <row r="360" spans="1:87" ht="15.6">
       <c r="A360" s="4">
         <v>359</v>
       </c>
@@ -40940,7 +40941,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="361" spans="1:87" hidden="1">
+    <row r="361" spans="1:87">
       <c r="A361" s="4">
         <v>360</v>
       </c>
@@ -41053,7 +41054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:87" hidden="1">
+    <row r="362" spans="1:87">
       <c r="A362" s="4">
         <v>361</v>
       </c>
@@ -41119,7 +41120,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="363" spans="1:87" hidden="1">
+    <row r="363" spans="1:87">
       <c r="A363" s="4">
         <v>362</v>
       </c>
@@ -41200,7 +41201,7 @@
       </c>
       <c r="BA363" s="184"/>
     </row>
-    <row r="364" spans="1:87" hidden="1">
+    <row r="364" spans="1:87">
       <c r="A364" s="4">
         <v>363</v>
       </c>
@@ -41313,7 +41314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:87" ht="15.6" hidden="1">
+    <row r="365" spans="1:87" ht="15.6">
       <c r="A365" s="4">
         <v>364</v>
       </c>
@@ -41411,7 +41412,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="366" spans="1:87" ht="15.6" hidden="1">
+    <row r="366" spans="1:87" ht="15.6">
       <c r="A366" s="4">
         <v>365</v>
       </c>
@@ -41507,7 +41508,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="367" spans="1:87" ht="15.6" hidden="1">
+    <row r="367" spans="1:87" ht="15.6">
       <c r="A367" s="4">
         <v>366</v>
       </c>
@@ -41522,7 +41523,7 @@
       </c>
       <c r="E367" s="1">
         <f t="shared" ca="1" si="26"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F367" s="1">
         <f t="shared" si="24"/>
@@ -41596,7 +41597,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="368" spans="1:87" hidden="1">
+    <row r="368" spans="1:87">
       <c r="A368" s="4">
         <v>367</v>
       </c>
@@ -41697,7 +41698,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="369" spans="1:53" hidden="1">
+    <row r="369" spans="1:53">
       <c r="A369" s="4">
         <v>368</v>
       </c>
@@ -41734,15 +41735,6 @@
       <c r="BA369" s="184"/>
     </row>
   </sheetData>
-  <autoFilter ref="C1:C369">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="CHU  Lille"/>
-        <filter val="CHU Lille"/>
-        <filter val="lille Catho"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -41750,18 +41742,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D87"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
     <col min="2" max="2" width="33" style="1" customWidth="1"/>
@@ -42715,10 +42707,10 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Foglio2"/>
   <dimension ref="A1:E164"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="36.44140625" style="49" customWidth="1"/>
     <col min="2" max="3" width="55.5546875" style="49" customWidth="1"/>
